--- a/backend/tests/reporting/output/findings.xlsx
+++ b/backend/tests/reporting/output/findings.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD8B1"/>
+        <bgColor rgb="00FFD8B1"/>
       </patternFill>
     </fill>
     <fill>
@@ -80,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -98,6 +104,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -465,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -546,179 +555,307 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>[FINDING - see module docstring] Every E-code should be correctly classified when entered in its real, natural product-label case</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Business Logic / Data Integrity</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Exercises the fuzzy-match step (step 2) using the exact capitalization a user would see on a real ingredient label -- not a pre-lowercased convenience string. 4 of 30 entries are confirmed broken by a case-sensitivity bug in the fuzzy matcher; see the module docstring for the full root-cause analysis with exact WRatio scores.</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>unit/test_ingredient_engine_matrix.py::test_ecode_matched_by_real_label_full_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>[CONFIRMED BUG] History should be reliably ordered newest-first, even for scans made within the same second</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Functional API / Business Logic</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Simulates the common case of a user scanning several products back-to-back (well within one second in an automated test, but this is also realistic for a fast human scanner or a barcode-gun-style flow).</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>A user who scans several products in quick succession sees their history in the wrong order.</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>add id DESC as a secondary sort key in routers/history.py: .order_by(desc(ScanHistory.scanned_at), desc(ScanHistory.id)).</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>functional/test_history_functional.py::test_history_ordered_newest_first</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>[FINDING] The barcode field has no format/character validation before being concatenated into the outbound Open Food Facts request URL</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Injection / Configuration</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>schemas/scan.py declares BarcodeRequest.barcode as a bare str (no regex/length constraint), and services/off_client.py builds the request URL via an f-string: f"{base_url}/{barcode}.json" -- not urljoin, not URL-encoded, not validated as numeric.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Low in this specific app (base_url is hardcoded to https://world.openfoodfacts.org, so this can only manipulate the PATH on that fixed host -- it is not a full SSRF to an arbitrary host). Still a real defect: if base_url or the request pattern ever changes, or if this pattern is copied to a future integration, unsanitized string concatenation into a URL is exactly the shape that becomes exploitable. Confirmed live: a barcode of "../../../etc/passwd" produces the literal outbound path ".../api/v2/product/../../../etc/passwd.json".</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Validate barcode format (EAN/UPC are numeric, 8-14 digits) with a Pydantic pattern constraint before it ever reaches off_client.</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>security/test_input_validation_injection.py::test_barcode_value_reaches_outbound_url_unsanitized</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>[FINDING] No X-Content-Type-Options / X-Frame-Options / HSTS / CSP headers</t>
+          <t>[FINDING] The barcode field has no format/character validation before being concatenated into the outbound Open Food Facts request URL</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Configuration / Security Headers</t>
+          <t>Injection / Configuration</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Confirms the current, undocumented state of the response headers on a plain JSON API response.</t>
+          <t>schemas/scan.py declares BarcodeRequest.barcode as a bare str (no regex/length constraint), and services/off_client.py builds the request URL via an f-string: f"{base_url}/{barcode}.json" -- not urljoin, not URL-encoded, not validated as numeric.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Low for a pure JSON API consumed by a known mobile/web client (there's no HTML rendering surface for clickjacking/MIME-sniffing to exploit directly here), but these are cheap, standard defense-in-depth headers and their absence should be a deliberate choice, not an oversight. HSTS in particular matters once this sits behind a public HTTPS endpoint (deploy notes mention Render, which terminates TLS at the edge -- confirm HSTS is added there or in this app).</t>
+          <t>Low in this specific app (base_url is hardcoded to https://world.openfoodfacts.org, so this can only manipulate the PATH on that fixed host -- it is not a full SSRF to an arbitrary host). Still a real defect: if base_url or the request pattern ever changes, or if this pattern is copied to a future integration, unsanitized string concatenation into a URL is exactly the shape that becomes exploitable. Confirmed live: a barcode of "../../../etc/passwd" produces the literal outbound path ".../api/v2/product/../../../etc/passwd.json".</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Add a small middleware (or starlette's SecurityHeaders pattern) setting X-Content-Type-Options: nosniff, X-Frame-Options: DENY, and Strict-Transport-Security in production.</t>
+          <t>Validate barcode format (EAN/UPC are numeric, 8-14 digits) with a Pydantic pattern constraint before it ever reaches off_client.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>security/test_configuration_headers.py::test_no_hardening_security_headers_present</t>
+          <t>security/test_input_validation_injection.py::test_barcode_value_reaches_outbound_url_unsanitized</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>[FINDING] /users/me and /history have no @limiter.limit(...) at all</t>
+          <t>[FINDING - see module docstring] The matcher should identify the CORRECT specific E-code entry, not just happen to land on the right status by coincidence</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Rate Limiting / Configuration</t>
+          <t>Business Logic / Data Integrity</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>main.py only wires the limiter's exception handler and state; routers/user.py and routers/history.py never import or apply @limiter. This test demonstrates the current (unlimited) behavior explicitly rather than leaving it undocumented.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Low -- both routers require a valid authenticated identity via get_current_user, so this isn't an anonymous-abuse vector the way an unlimited /scan/analyse would be. Still worth tracking: a compromised or leaked token currently has no throttle on read/write volume against a user's own data (e.g. scripted DELETE-then-recreate loops, or bulk history scraping).</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Consider a generous per-user rate limit (e.g. 120/minute) on authenticated routes as defense in depth, matching the pattern already established for /scan/*.</t>
-        </is>
-      </c>
+          <t>Stricter than test_ecode_matched_by_real_label_full_name -- checks that the E-code's own full_name appears in the result reason (proof the right entry was actually selected), not just that the final status string happens to match. This catches one additional casualty (E412 "Guar Gum") that test_ecode_matched_by_real_label_full_name misses, because Guar Gum's broken match happens to fall through to a "safe" default that coincidentally equals its real status -- the identification is still broken, it's just invisible if you only check the final status.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>security/test_rate_limiting.py::test_authenticated_endpoints_have_no_rate_limit_configured</t>
+          <t>unit/test_ingredient_engine_matrix.py::test_ecode_actually_identified_by_real_label_full_name</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>[FINDING] No X-Content-Type-Options / X-Frame-Options / HSTS / CSP headers</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Configuration / Security Headers</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Confirms the current, undocumented state of the response headers on a plain JSON API response.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Low for a pure JSON API consumed by a known mobile/web client (there's no HTML rendering surface for clickjacking/MIME-sniffing to exploit directly here), but these are cheap, standard defense-in-depth headers and their absence should be a deliberate choice, not an oversight. HSTS in particular matters once this sits behind a public HTTPS endpoint (deploy notes mention Render, which terminates TLS at the edge -- confirm HSTS is added there or in this app).</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Add a small middleware (or starlette's SecurityHeaders pattern) setting X-Content-Type-Options: nosniff, X-Frame-Options: DENY, and Strict-Transport-Security in production.</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>security/test_configuration_headers.py::test_no_hardening_security_headers_present</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>[FINDING] /users/me and /history have no @limiter.limit(...) at all</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Rate Limiting / Configuration</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>main.py only wires the limiter's exception handler and state; routers/user.py and routers/history.py never import or apply @limiter. This test demonstrates the current (unlimited) behavior explicitly rather than leaving it undocumented.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Low -- both routers require a valid authenticated identity via get_current_user, so this isn't an anonymous-abuse vector the way an unlimited /scan/analyse would be. Still worth tracking: a compromised or leaked token currently has no throttle on read/write volume against a user's own data (e.g. scripted DELETE-then-recreate loops, or bulk history scraping).</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Consider a generous per-user rate limit (e.g. 120/minute) on authenticated routes as defense in depth, matching the pattern already established for /scan/*.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>security/test_rate_limiting.py::test_authenticated_endpoints_have_no_rate_limit_configured</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>[FINDING] A condition name not in the hardcoded set (Diabetes/ Hypertension/High Cholesterol) is silently ignored, deducting nothing</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Business Logic / Scoring Algorithm</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>schemas/user.py's "conditions" field is a free-text List[str] with no validation against a fixed enum -- a user (or a future frontend update) could save "Celiac Disease" or "Kidney Disease" and it would simply never affect scoring, with no error or warning anywhere.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Low-to-Medium. Not a security issue, but a silent correctness gap: the scoring algorithm's condition-awareness only covers 3 hardcoded conditions no matter what the user actually saves.</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>either constrain "conditions" to a known enum at the schema level, or make calculate_hs_score's condition matching data-driven instead of three hardcoded if-blocks.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>unit/test_ingredient_engine_matrix.py::test_unrecognized_condition_name_is_silently_ignored</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>[FINDING] An ingredient classified "safe" by analyze_ingredients can still be scored down by calculate_hs_score if its name contains "sugar", "syrup", "palm oil", or "fructose"</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Business Logic / Scoring Algorithm</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>calculate_hs_score's additive-penalty loop has a SEPARATE, independent keyword check -- `if any(x in name_lower for x in ["sugar", "syrup", "palm oil", "fructose"])` -- that applies regardless of the ingredient's status field. A plain ingredient named "sugar" is classified "safe" by analyze_ingredients (it's not in ecodes.json or harmful_keywords), but calculate_hs_score still deducts points for it via this separate name-based check. Confirmed directly: ["water","salt","sugar"] at nova_class=1 scores 92, not 100, solely because of "sugar" appearing third in the list.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Not a security issue, and arguably reasonable product behavior (added sugar probably SHOULD cost points even if it's not flagged as an "unsafe" ingredient) -- but it's undocumented, inconsistent with the ingredient's own reported status ("No major concerns found." next to a score deduction is confusing for a user), and worth being a deliberate, documented design choice rather than an incidental side effect discovered by testing.</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>unit/test_ingredient_engine_matrix.py::test_safe_status_ingredient_still_penalized_if_name_contains_sugar_keyword</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
           <t>Informational</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>[INFORMATIONAL] /docs and /openapi.json are exposed with default FastAPI settings</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Configuration / Information Disclosure</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Document the current state -- FastAPI's interactive docs are not disabled (no docs_url=None / openapi_url=None in main.py's FastAPI(...) constructor).</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Informational only. A fully-documented schema of your own public API is not itself a vulnerability, but it does hand an attacker a complete endpoint/parameter map for free and should be a deliberate choice for a production deployment, not a default left over from development.</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>security/test_configuration_headers.py::test_openapi_schema_is_reachable</t>
         </is>
